--- a/Team-Data/2008-09/4-9-2008-09.xlsx
+++ b/Team-Data/2008-09/4-9-2008-09.xlsx
@@ -50,7 +50,6 @@
       <right style="thin"/>
       <top style="thin"/>
       <bottom style="thin"/>
-      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
@@ -66,6 +65,74 @@
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -739,7 +806,7 @@
         <v>1.7</v>
       </c>
       <c r="AD2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AE2" t="n">
         <v>12</v>
@@ -760,7 +827,7 @@
         <v>24</v>
       </c>
       <c r="AK2" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AL2" t="n">
         <v>8</v>
@@ -772,10 +839,10 @@
         <v>17</v>
       </c>
       <c r="AO2" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AP2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AQ2" t="n">
         <v>29</v>
@@ -826,7 +893,7 @@
       </c>
       <c r="BF2" t="inlineStr">
         <is>
-          <t>4-9-2008-09</t>
+          <t>2009-04-09</t>
         </is>
       </c>
     </row>
@@ -843,16 +910,16 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="E3" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="F3" t="n">
         <v>19</v>
       </c>
       <c r="G3" t="n">
-        <v>0.753</v>
+        <v>0.756</v>
       </c>
       <c r="H3" t="n">
         <v>48.5</v>
@@ -861,28 +928,28 @@
         <v>37.5</v>
       </c>
       <c r="J3" t="n">
-        <v>77.09999999999999</v>
+        <v>77</v>
       </c>
       <c r="K3" t="n">
-        <v>0.487</v>
+        <v>0.486</v>
       </c>
       <c r="L3" t="n">
         <v>6.5</v>
       </c>
       <c r="M3" t="n">
-        <v>16.6</v>
+        <v>16.5</v>
       </c>
       <c r="N3" t="n">
-        <v>0.394</v>
+        <v>0.392</v>
       </c>
       <c r="O3" t="n">
         <v>19.6</v>
       </c>
       <c r="P3" t="n">
-        <v>25.4</v>
+        <v>25.5</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.771</v>
+        <v>0.768</v>
       </c>
       <c r="R3" t="n">
         <v>10.6</v>
@@ -891,10 +958,10 @@
         <v>31.8</v>
       </c>
       <c r="T3" t="n">
-        <v>42.4</v>
+        <v>42.3</v>
       </c>
       <c r="U3" t="n">
-        <v>22.8</v>
+        <v>22.7</v>
       </c>
       <c r="V3" t="n">
         <v>15.7</v>
@@ -903,25 +970,25 @@
         <v>7.6</v>
       </c>
       <c r="X3" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="Y3" t="n">
         <v>4.7</v>
       </c>
       <c r="Z3" t="n">
-        <v>23</v>
+        <v>23.1</v>
       </c>
       <c r="AA3" t="n">
         <v>22.2</v>
       </c>
       <c r="AB3" t="n">
-        <v>101.2</v>
+        <v>101</v>
       </c>
       <c r="AC3" t="n">
         <v>8.1</v>
       </c>
       <c r="AD3" t="n">
-        <v>28</v>
+        <v>7</v>
       </c>
       <c r="AE3" t="n">
         <v>3</v>
@@ -954,13 +1021,13 @@
         <v>1</v>
       </c>
       <c r="AO3" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AP3" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AQ3" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AR3" t="n">
         <v>21</v>
@@ -969,7 +1036,7 @@
         <v>5</v>
       </c>
       <c r="AT3" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AU3" t="n">
         <v>4</v>
@@ -990,10 +1057,10 @@
         <v>27</v>
       </c>
       <c r="BA3" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="BB3" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="BC3" t="n">
         <v>2</v>
@@ -1008,7 +1075,7 @@
       </c>
       <c r="BF3" t="inlineStr">
         <is>
-          <t>4-9-2008-09</t>
+          <t>2009-04-09</t>
         </is>
       </c>
     </row>
@@ -1160,7 +1227,7 @@
         <v>27</v>
       </c>
       <c r="AW4" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AX4" t="n">
         <v>14</v>
@@ -1190,7 +1257,7 @@
       </c>
       <c r="BF4" t="inlineStr">
         <is>
-          <t>4-9-2008-09</t>
+          <t>2009-04-09</t>
         </is>
       </c>
     </row>
@@ -1222,10 +1289,10 @@
         <v>48.6</v>
       </c>
       <c r="I5" t="n">
-        <v>38.2</v>
+        <v>38.1</v>
       </c>
       <c r="J5" t="n">
-        <v>83.59999999999999</v>
+        <v>83.5</v>
       </c>
       <c r="K5" t="n">
         <v>0.456</v>
@@ -1234,22 +1301,22 @@
         <v>6</v>
       </c>
       <c r="M5" t="n">
-        <v>15.7</v>
+        <v>15.6</v>
       </c>
       <c r="N5" t="n">
-        <v>0.382</v>
+        <v>0.383</v>
       </c>
       <c r="O5" t="n">
-        <v>19.8</v>
+        <v>20</v>
       </c>
       <c r="P5" t="n">
-        <v>24.9</v>
+        <v>25.2</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.797</v>
+        <v>0.794</v>
       </c>
       <c r="R5" t="n">
-        <v>11.9</v>
+        <v>12</v>
       </c>
       <c r="S5" t="n">
         <v>30.4</v>
@@ -1261,7 +1328,7 @@
         <v>21</v>
       </c>
       <c r="V5" t="n">
-        <v>14.7</v>
+        <v>14.8</v>
       </c>
       <c r="W5" t="n">
         <v>7.5</v>
@@ -1276,13 +1343,13 @@
         <v>20.9</v>
       </c>
       <c r="AA5" t="n">
-        <v>20.7</v>
+        <v>20.8</v>
       </c>
       <c r="AB5" t="n">
-        <v>102.2</v>
+        <v>102.1</v>
       </c>
       <c r="AC5" t="n">
-        <v>-0.4</v>
+        <v>-0.5</v>
       </c>
       <c r="AD5" t="n">
         <v>7</v>
@@ -1312,16 +1379,16 @@
         <v>23</v>
       </c>
       <c r="AM5" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AN5" t="n">
+        <v>5</v>
+      </c>
+      <c r="AO5" t="n">
         <v>6</v>
       </c>
-      <c r="AO5" t="n">
-        <v>7</v>
-      </c>
       <c r="AP5" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AQ5" t="n">
         <v>7</v>
@@ -1333,13 +1400,13 @@
         <v>14</v>
       </c>
       <c r="AT5" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AU5" t="n">
         <v>14</v>
       </c>
       <c r="AV5" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AW5" t="n">
         <v>9</v>
@@ -1372,7 +1439,7 @@
       </c>
       <c r="BF5" t="inlineStr">
         <is>
-          <t>4-9-2008-09</t>
+          <t>2009-04-09</t>
         </is>
       </c>
     </row>
@@ -1389,61 +1456,61 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="E6" t="n">
         <v>63</v>
       </c>
       <c r="F6" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G6" t="n">
-        <v>0.8179999999999999</v>
+        <v>0.8080000000000001</v>
       </c>
       <c r="H6" t="n">
         <v>48.2</v>
       </c>
       <c r="I6" t="n">
-        <v>36.8</v>
+        <v>36.7</v>
       </c>
       <c r="J6" t="n">
-        <v>78.7</v>
+        <v>78.59999999999999</v>
       </c>
       <c r="K6" t="n">
         <v>0.467</v>
       </c>
       <c r="L6" t="n">
-        <v>8</v>
+        <v>7.9</v>
       </c>
       <c r="M6" t="n">
-        <v>20.4</v>
+        <v>20.3</v>
       </c>
       <c r="N6" t="n">
-        <v>0.39</v>
+        <v>0.388</v>
       </c>
       <c r="O6" t="n">
-        <v>18.5</v>
+        <v>18.6</v>
       </c>
       <c r="P6" t="n">
-        <v>24.5</v>
+        <v>24.6</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.757</v>
+        <v>0.756</v>
       </c>
       <c r="R6" t="n">
         <v>10.7</v>
       </c>
       <c r="S6" t="n">
-        <v>31.4</v>
+        <v>31.5</v>
       </c>
       <c r="T6" t="n">
         <v>42.2</v>
       </c>
       <c r="U6" t="n">
-        <v>20.2</v>
+        <v>20.1</v>
       </c>
       <c r="V6" t="n">
-        <v>12.5</v>
+        <v>12.7</v>
       </c>
       <c r="W6" t="n">
         <v>7.3</v>
@@ -1452,22 +1519,22 @@
         <v>5.3</v>
       </c>
       <c r="Y6" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="Z6" t="n">
-        <v>20</v>
+        <v>20.1</v>
       </c>
       <c r="AA6" t="n">
-        <v>20.2</v>
+        <v>20.3</v>
       </c>
       <c r="AB6" t="n">
-        <v>100</v>
+        <v>99.8</v>
       </c>
       <c r="AC6" t="n">
-        <v>8.9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD6" t="n">
-        <v>28</v>
+        <v>7</v>
       </c>
       <c r="AE6" t="n">
         <v>1</v>
@@ -1491,7 +1558,7 @@
         <v>6</v>
       </c>
       <c r="AL6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AM6" t="n">
         <v>5</v>
@@ -1500,13 +1567,13 @@
         <v>2</v>
       </c>
       <c r="AO6" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AP6" t="n">
         <v>15</v>
       </c>
       <c r="AQ6" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AR6" t="n">
         <v>19</v>
@@ -1527,7 +1594,7 @@
         <v>16</v>
       </c>
       <c r="AX6" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AY6" t="n">
         <v>4</v>
@@ -1536,7 +1603,7 @@
         <v>6</v>
       </c>
       <c r="BA6" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="BB6" t="n">
         <v>13</v>
@@ -1554,7 +1621,7 @@
       </c>
       <c r="BF6" t="inlineStr">
         <is>
-          <t>4-9-2008-09</t>
+          <t>2009-04-09</t>
         </is>
       </c>
     </row>
@@ -1694,7 +1761,7 @@
         <v>13</v>
       </c>
       <c r="AS7" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AT7" t="n">
         <v>5</v>
@@ -1703,13 +1770,13 @@
         <v>9</v>
       </c>
       <c r="AV7" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AW7" t="n">
         <v>15</v>
       </c>
       <c r="AX7" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AY7" t="n">
         <v>7</v>
@@ -1736,7 +1803,7 @@
       </c>
       <c r="BF7" t="inlineStr">
         <is>
-          <t>4-9-2008-09</t>
+          <t>2009-04-09</t>
         </is>
       </c>
     </row>
@@ -1753,16 +1820,16 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E8" t="n">
         <v>53</v>
       </c>
       <c r="F8" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G8" t="n">
-        <v>0.663</v>
+        <v>0.671</v>
       </c>
       <c r="H8" t="n">
         <v>48.1</v>
@@ -1783,25 +1850,25 @@
         <v>17.9</v>
       </c>
       <c r="N8" t="n">
-        <v>0.37</v>
+        <v>0.372</v>
       </c>
       <c r="O8" t="n">
         <v>23.1</v>
       </c>
       <c r="P8" t="n">
-        <v>30.4</v>
+        <v>30.5</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.759</v>
+        <v>0.758</v>
       </c>
       <c r="R8" t="n">
         <v>11</v>
       </c>
       <c r="S8" t="n">
-        <v>30.6</v>
+        <v>30.5</v>
       </c>
       <c r="T8" t="n">
-        <v>41.6</v>
+        <v>41.5</v>
       </c>
       <c r="U8" t="n">
         <v>22.3</v>
@@ -1819,16 +1886,16 @@
         <v>5.5</v>
       </c>
       <c r="Z8" t="n">
-        <v>23</v>
+        <v>22.9</v>
       </c>
       <c r="AA8" t="n">
-        <v>23.8</v>
+        <v>23.7</v>
       </c>
       <c r="AB8" t="n">
         <v>104.5</v>
       </c>
       <c r="AC8" t="n">
-        <v>3.6</v>
+        <v>3.8</v>
       </c>
       <c r="AD8" t="n">
         <v>1</v>
@@ -1855,7 +1922,7 @@
         <v>5</v>
       </c>
       <c r="AL8" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AM8" t="n">
         <v>18</v>
@@ -1906,7 +1973,7 @@
         <v>6</v>
       </c>
       <c r="BC8" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="BD8" t="n">
         <v>10</v>
@@ -1918,7 +1985,7 @@
       </c>
       <c r="BF8" t="inlineStr">
         <is>
-          <t>4-9-2008-09</t>
+          <t>2009-04-09</t>
         </is>
       </c>
     </row>
@@ -2025,7 +2092,7 @@
         <v>16</v>
       </c>
       <c r="AH9" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AI9" t="n">
         <v>22</v>
@@ -2061,7 +2128,7 @@
         <v>18</v>
       </c>
       <c r="AT9" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AU9" t="n">
         <v>16</v>
@@ -2100,7 +2167,7 @@
       </c>
       <c r="BF9" t="inlineStr">
         <is>
-          <t>4-9-2008-09</t>
+          <t>2009-04-09</t>
         </is>
       </c>
     </row>
@@ -2216,7 +2283,7 @@
         <v>3</v>
       </c>
       <c r="AK10" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AL10" t="n">
         <v>15</v>
@@ -2246,10 +2313,10 @@
         <v>10</v>
       </c>
       <c r="AU10" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AV10" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AW10" t="n">
         <v>6</v>
@@ -2282,7 +2349,7 @@
       </c>
       <c r="BF10" t="inlineStr">
         <is>
-          <t>4-9-2008-09</t>
+          <t>2009-04-09</t>
         </is>
       </c>
     </row>
@@ -2299,43 +2366,43 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="E11" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="F11" t="n">
         <v>28</v>
       </c>
       <c r="G11" t="n">
-        <v>0.646</v>
+        <v>0.641</v>
       </c>
       <c r="H11" t="n">
         <v>48.3</v>
       </c>
       <c r="I11" t="n">
-        <v>36.1</v>
+        <v>36</v>
       </c>
       <c r="J11" t="n">
-        <v>79.59999999999999</v>
+        <v>79.5</v>
       </c>
       <c r="K11" t="n">
-        <v>0.453</v>
+        <v>0.452</v>
       </c>
       <c r="L11" t="n">
-        <v>7.7</v>
+        <v>7.6</v>
       </c>
       <c r="M11" t="n">
         <v>20.2</v>
       </c>
       <c r="N11" t="n">
-        <v>0.378</v>
+        <v>0.376</v>
       </c>
       <c r="O11" t="n">
-        <v>18.7</v>
+        <v>18.8</v>
       </c>
       <c r="P11" t="n">
-        <v>23.3</v>
+        <v>23.4</v>
       </c>
       <c r="Q11" t="n">
         <v>0.803</v>
@@ -2347,7 +2414,7 @@
         <v>32.5</v>
       </c>
       <c r="T11" t="n">
-        <v>42.9</v>
+        <v>43</v>
       </c>
       <c r="U11" t="n">
         <v>20.3</v>
@@ -2359,46 +2426,46 @@
         <v>6.7</v>
       </c>
       <c r="X11" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="Y11" t="n">
         <v>5.4</v>
       </c>
       <c r="Z11" t="n">
-        <v>18.9</v>
+        <v>19</v>
       </c>
       <c r="AA11" t="n">
-        <v>20.6</v>
+        <v>20.7</v>
       </c>
       <c r="AB11" t="n">
-        <v>98.59999999999999</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="AC11" t="n">
-        <v>4</v>
+        <v>3.8</v>
       </c>
       <c r="AD11" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="AE11" t="n">
         <v>6</v>
       </c>
       <c r="AF11" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AG11" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AH11" t="n">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="AI11" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AJ11" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AK11" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AL11" t="n">
         <v>6</v>
@@ -2410,7 +2477,7 @@
         <v>8</v>
       </c>
       <c r="AO11" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AP11" t="n">
         <v>21</v>
@@ -2422,7 +2489,7 @@
         <v>22</v>
       </c>
       <c r="AS11" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AT11" t="n">
         <v>4</v>
@@ -2446,13 +2513,13 @@
         <v>2</v>
       </c>
       <c r="BA11" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="BB11" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="BC11" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="BD11" t="n">
         <v>10</v>
@@ -2464,7 +2531,7 @@
       </c>
       <c r="BF11" t="inlineStr">
         <is>
-          <t>4-9-2008-09</t>
+          <t>2009-04-09</t>
         </is>
       </c>
     </row>
@@ -2571,7 +2638,7 @@
         <v>19</v>
       </c>
       <c r="AH12" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AI12" t="n">
         <v>4</v>
@@ -2619,7 +2686,7 @@
         <v>24</v>
       </c>
       <c r="AX12" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AY12" t="n">
         <v>25</v>
@@ -2628,7 +2695,7 @@
         <v>28</v>
       </c>
       <c r="BA12" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="BB12" t="n">
         <v>5</v>
@@ -2646,7 +2713,7 @@
       </c>
       <c r="BF12" t="inlineStr">
         <is>
-          <t>4-9-2008-09</t>
+          <t>2009-04-09</t>
         </is>
       </c>
     </row>
@@ -2753,10 +2820,10 @@
         <v>28</v>
       </c>
       <c r="AH13" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AI13" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AJ13" t="n">
         <v>10</v>
@@ -2765,13 +2832,13 @@
         <v>30</v>
       </c>
       <c r="AL13" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AM13" t="n">
         <v>16</v>
       </c>
       <c r="AN13" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AO13" t="n">
         <v>28</v>
@@ -2786,7 +2853,7 @@
         <v>15</v>
       </c>
       <c r="AS13" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AT13" t="n">
         <v>26</v>
@@ -2828,7 +2895,7 @@
       </c>
       <c r="BF13" t="inlineStr">
         <is>
-          <t>4-9-2008-09</t>
+          <t>2009-04-09</t>
         </is>
       </c>
     </row>
@@ -2863,37 +2930,37 @@
         <v>40.3</v>
       </c>
       <c r="J14" t="n">
-        <v>85.2</v>
+        <v>85.09999999999999</v>
       </c>
       <c r="K14" t="n">
-        <v>0.473</v>
+        <v>0.474</v>
       </c>
       <c r="L14" t="n">
         <v>6.7</v>
       </c>
       <c r="M14" t="n">
-        <v>18.7</v>
+        <v>18.5</v>
       </c>
       <c r="N14" t="n">
-        <v>0.358</v>
+        <v>0.362</v>
       </c>
       <c r="O14" t="n">
-        <v>19.8</v>
+        <v>19.5</v>
       </c>
       <c r="P14" t="n">
-        <v>25.8</v>
+        <v>25.4</v>
       </c>
       <c r="Q14" t="n">
         <v>0.768</v>
       </c>
       <c r="R14" t="n">
-        <v>12.5</v>
+        <v>12.4</v>
       </c>
       <c r="S14" t="n">
         <v>31.6</v>
       </c>
       <c r="T14" t="n">
-        <v>44.1</v>
+        <v>44</v>
       </c>
       <c r="U14" t="n">
         <v>23.2</v>
@@ -2905,22 +2972,22 @@
         <v>8.800000000000001</v>
       </c>
       <c r="X14" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="Y14" t="n">
         <v>4.8</v>
       </c>
       <c r="Z14" t="n">
-        <v>20.5</v>
+        <v>20.4</v>
       </c>
       <c r="AA14" t="n">
-        <v>22.2</v>
+        <v>22.1</v>
       </c>
       <c r="AB14" t="n">
-        <v>107.1</v>
+        <v>106.9</v>
       </c>
       <c r="AC14" t="n">
-        <v>7.5</v>
+        <v>7.6</v>
       </c>
       <c r="AD14" t="n">
         <v>7</v>
@@ -2950,16 +3017,16 @@
         <v>16</v>
       </c>
       <c r="AM14" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AN14" t="n">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="AO14" t="n">
+        <v>12</v>
+      </c>
+      <c r="AP14" t="n">
         <v>10</v>
-      </c>
-      <c r="AP14" t="n">
-        <v>8</v>
       </c>
       <c r="AQ14" t="n">
         <v>16</v>
@@ -2968,13 +3035,13 @@
         <v>3</v>
       </c>
       <c r="AS14" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AT14" t="n">
         <v>1</v>
       </c>
       <c r="AU14" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AV14" t="n">
         <v>11</v>
@@ -2983,7 +3050,7 @@
         <v>2</v>
       </c>
       <c r="AX14" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AY14" t="n">
         <v>14</v>
@@ -2992,7 +3059,7 @@
         <v>12</v>
       </c>
       <c r="BA14" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="BB14" t="n">
         <v>3</v>
@@ -3010,7 +3077,7 @@
       </c>
       <c r="BF14" t="inlineStr">
         <is>
-          <t>4-9-2008-09</t>
+          <t>2009-04-09</t>
         </is>
       </c>
     </row>
@@ -3126,7 +3193,7 @@
         <v>29</v>
       </c>
       <c r="AK15" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AL15" t="n">
         <v>27</v>
@@ -3135,16 +3202,16 @@
         <v>27</v>
       </c>
       <c r="AN15" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AO15" t="n">
         <v>13</v>
       </c>
       <c r="AP15" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AQ15" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AR15" t="n">
         <v>23</v>
@@ -3192,7 +3259,7 @@
       </c>
       <c r="BF15" t="inlineStr">
         <is>
-          <t>4-9-2008-09</t>
+          <t>2009-04-09</t>
         </is>
       </c>
     </row>
@@ -3374,7 +3441,7 @@
       </c>
       <c r="BF16" t="inlineStr">
         <is>
-          <t>4-9-2008-09</t>
+          <t>2009-04-09</t>
         </is>
       </c>
     </row>
@@ -3391,16 +3458,16 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="E17" t="n">
         <v>32</v>
       </c>
       <c r="F17" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="G17" t="n">
-        <v>0.41</v>
+        <v>0.405</v>
       </c>
       <c r="H17" t="n">
         <v>48.3</v>
@@ -3412,40 +3479,40 @@
         <v>82.2</v>
       </c>
       <c r="K17" t="n">
-        <v>0.444</v>
+        <v>0.445</v>
       </c>
       <c r="L17" t="n">
         <v>6.2</v>
       </c>
       <c r="M17" t="n">
-        <v>17.1</v>
+        <v>17</v>
       </c>
       <c r="N17" t="n">
-        <v>0.361</v>
+        <v>0.362</v>
       </c>
       <c r="O17" t="n">
-        <v>19.8</v>
+        <v>19.7</v>
       </c>
       <c r="P17" t="n">
-        <v>25.4</v>
+        <v>25.3</v>
       </c>
       <c r="Q17" t="n">
-        <v>0.781</v>
+        <v>0.78</v>
       </c>
       <c r="R17" t="n">
         <v>11.9</v>
       </c>
       <c r="S17" t="n">
-        <v>28.8</v>
+        <v>28.7</v>
       </c>
       <c r="T17" t="n">
-        <v>40.7</v>
+        <v>40.5</v>
       </c>
       <c r="U17" t="n">
         <v>21.7</v>
       </c>
       <c r="V17" t="n">
-        <v>14.1</v>
+        <v>14.2</v>
       </c>
       <c r="W17" t="n">
         <v>7.4</v>
@@ -3460,28 +3527,28 @@
         <v>24.3</v>
       </c>
       <c r="AA17" t="n">
-        <v>22.7</v>
+        <v>22.6</v>
       </c>
       <c r="AB17" t="n">
-        <v>99.09999999999999</v>
+        <v>99</v>
       </c>
       <c r="AC17" t="n">
-        <v>-1.3</v>
+        <v>-1.5</v>
       </c>
       <c r="AD17" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="AE17" t="n">
         <v>20</v>
       </c>
       <c r="AF17" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AG17" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AH17" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AI17" t="n">
         <v>18</v>
@@ -3502,19 +3569,19 @@
         <v>19</v>
       </c>
       <c r="AO17" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AP17" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AQ17" t="n">
         <v>11</v>
       </c>
       <c r="AR17" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AS17" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="AT17" t="n">
         <v>20</v>
@@ -3523,10 +3590,10 @@
         <v>8</v>
       </c>
       <c r="AV17" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AW17" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AX17" t="n">
         <v>29</v>
@@ -3556,7 +3623,7 @@
       </c>
       <c r="BF17" t="inlineStr">
         <is>
-          <t>4-9-2008-09</t>
+          <t>2009-04-09</t>
         </is>
       </c>
     </row>
@@ -3651,7 +3718,7 @@
         <v>-4.8</v>
       </c>
       <c r="AD18" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AE18" t="n">
         <v>25</v>
@@ -3663,7 +3730,7 @@
         <v>25</v>
       </c>
       <c r="AH18" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AI18" t="n">
         <v>20</v>
@@ -3678,7 +3745,7 @@
         <v>19</v>
       </c>
       <c r="AM18" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AN18" t="n">
         <v>24</v>
@@ -3690,7 +3757,7 @@
         <v>18</v>
       </c>
       <c r="AQ18" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AR18" t="n">
         <v>6</v>
@@ -3705,7 +3772,7 @@
         <v>17</v>
       </c>
       <c r="AV18" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AW18" t="n">
         <v>28</v>
@@ -3738,7 +3805,7 @@
       </c>
       <c r="BF18" t="inlineStr">
         <is>
-          <t>4-9-2008-09</t>
+          <t>2009-04-09</t>
         </is>
       </c>
     </row>
@@ -3845,7 +3912,7 @@
         <v>20</v>
       </c>
       <c r="AH19" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AI19" t="n">
         <v>26</v>
@@ -3857,7 +3924,7 @@
         <v>25</v>
       </c>
       <c r="AL19" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AM19" t="n">
         <v>3</v>
@@ -3902,10 +3969,10 @@
         <v>25</v>
       </c>
       <c r="BA19" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="BB19" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="BC19" t="n">
         <v>21</v>
@@ -3920,7 +3987,7 @@
       </c>
       <c r="BF19" t="inlineStr">
         <is>
-          <t>4-9-2008-09</t>
+          <t>2009-04-09</t>
         </is>
       </c>
     </row>
@@ -4042,7 +4109,7 @@
         <v>13</v>
       </c>
       <c r="AM20" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AN20" t="n">
         <v>16</v>
@@ -4102,7 +4169,7 @@
       </c>
       <c r="BF20" t="inlineStr">
         <is>
-          <t>4-9-2008-09</t>
+          <t>2009-04-09</t>
         </is>
       </c>
     </row>
@@ -4197,7 +4264,7 @@
         <v>-3</v>
       </c>
       <c r="AD21" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AE21" t="n">
         <v>22</v>
@@ -4209,7 +4276,7 @@
         <v>23</v>
       </c>
       <c r="AH21" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AI21" t="n">
         <v>5</v>
@@ -4227,7 +4294,7 @@
         <v>1</v>
       </c>
       <c r="AN21" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="AO21" t="n">
         <v>25</v>
@@ -4254,7 +4321,7 @@
         <v>19</v>
       </c>
       <c r="AW21" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AX21" t="n">
         <v>30</v>
@@ -4263,7 +4330,7 @@
         <v>22</v>
       </c>
       <c r="AZ21" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="BA21" t="n">
         <v>29</v>
@@ -4284,7 +4351,7 @@
       </c>
       <c r="BF21" t="inlineStr">
         <is>
-          <t>4-9-2008-09</t>
+          <t>2009-04-09</t>
         </is>
       </c>
     </row>
@@ -4412,10 +4479,10 @@
         <v>28</v>
       </c>
       <c r="AO22" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AP22" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AQ22" t="n">
         <v>9</v>
@@ -4466,7 +4533,7 @@
       </c>
       <c r="BF22" t="inlineStr">
         <is>
-          <t>4-9-2008-09</t>
+          <t>2009-04-09</t>
         </is>
       </c>
     </row>
@@ -4564,7 +4631,7 @@
         <v>7</v>
       </c>
       <c r="AE23" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AF23" t="n">
         <v>4</v>
@@ -4573,7 +4640,7 @@
         <v>4</v>
       </c>
       <c r="AH23" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AI23" t="n">
         <v>26</v>
@@ -4594,7 +4661,7 @@
         <v>4</v>
       </c>
       <c r="AO23" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="AP23" t="n">
         <v>4</v>
@@ -4618,7 +4685,7 @@
         <v>13</v>
       </c>
       <c r="AW23" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AX23" t="n">
         <v>6</v>
@@ -4648,7 +4715,7 @@
       </c>
       <c r="BF23" t="inlineStr">
         <is>
-          <t>4-9-2008-09</t>
+          <t>2009-04-09</t>
         </is>
       </c>
     </row>
@@ -4665,16 +4732,16 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="E24" t="n">
         <v>40</v>
       </c>
       <c r="F24" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="G24" t="n">
-        <v>0.513</v>
+        <v>0.519</v>
       </c>
       <c r="H24" t="n">
         <v>48.1</v>
@@ -4683,28 +4750,28 @@
         <v>36.6</v>
       </c>
       <c r="J24" t="n">
-        <v>79.8</v>
+        <v>79.90000000000001</v>
       </c>
       <c r="K24" t="n">
-        <v>0.459</v>
+        <v>0.458</v>
       </c>
       <c r="L24" t="n">
         <v>4.2</v>
       </c>
       <c r="M24" t="n">
-        <v>13.1</v>
+        <v>13.2</v>
       </c>
       <c r="N24" t="n">
-        <v>0.319</v>
+        <v>0.316</v>
       </c>
       <c r="O24" t="n">
-        <v>19.8</v>
+        <v>19.9</v>
       </c>
       <c r="P24" t="n">
         <v>26.7</v>
       </c>
       <c r="Q24" t="n">
-        <v>0.743</v>
+        <v>0.745</v>
       </c>
       <c r="R24" t="n">
         <v>12.6</v>
@@ -4713,7 +4780,7 @@
         <v>28.7</v>
       </c>
       <c r="T24" t="n">
-        <v>41.3</v>
+        <v>41.4</v>
       </c>
       <c r="U24" t="n">
         <v>20.2</v>
@@ -4731,7 +4798,7 @@
         <v>4.8</v>
       </c>
       <c r="Z24" t="n">
-        <v>20.2</v>
+        <v>20.3</v>
       </c>
       <c r="AA24" t="n">
         <v>21.6</v>
@@ -4740,16 +4807,16 @@
         <v>97.2</v>
       </c>
       <c r="AC24" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="AD24" t="n">
-        <v>7</v>
+        <v>29</v>
       </c>
       <c r="AE24" t="n">
         <v>15</v>
       </c>
       <c r="AF24" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AG24" t="n">
         <v>15</v>
@@ -4764,7 +4831,7 @@
         <v>19</v>
       </c>
       <c r="AK24" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="AL24" t="n">
         <v>29</v>
@@ -4776,7 +4843,7 @@
         <v>30</v>
       </c>
       <c r="AO24" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AP24" t="n">
         <v>6</v>
@@ -4788,16 +4855,16 @@
         <v>2</v>
       </c>
       <c r="AS24" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AT24" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AU24" t="n">
         <v>22</v>
       </c>
       <c r="AV24" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AW24" t="n">
         <v>5</v>
@@ -4830,7 +4897,7 @@
       </c>
       <c r="BF24" t="inlineStr">
         <is>
-          <t>4-9-2008-09</t>
+          <t>2009-04-09</t>
         </is>
       </c>
     </row>
@@ -4937,7 +5004,7 @@
         <v>13</v>
       </c>
       <c r="AH25" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AI25" t="n">
         <v>1</v>
@@ -4955,7 +5022,7 @@
         <v>19</v>
       </c>
       <c r="AN25" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AO25" t="n">
         <v>5</v>
@@ -5012,7 +5079,7 @@
       </c>
       <c r="BF25" t="inlineStr">
         <is>
-          <t>4-9-2008-09</t>
+          <t>2009-04-09</t>
         </is>
       </c>
     </row>
@@ -5029,28 +5096,28 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="E26" t="n">
         <v>50</v>
       </c>
       <c r="F26" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="G26" t="n">
-        <v>0.649</v>
+        <v>0.641</v>
       </c>
       <c r="H26" t="n">
         <v>48.4</v>
       </c>
       <c r="I26" t="n">
-        <v>36.9</v>
+        <v>36.8</v>
       </c>
       <c r="J26" t="n">
-        <v>79.09999999999999</v>
+        <v>79.2</v>
       </c>
       <c r="K26" t="n">
-        <v>0.466</v>
+        <v>0.464</v>
       </c>
       <c r="L26" t="n">
         <v>7.2</v>
@@ -5059,16 +5126,16 @@
         <v>18.9</v>
       </c>
       <c r="N26" t="n">
-        <v>0.381</v>
+        <v>0.382</v>
       </c>
       <c r="O26" t="n">
-        <v>18.7</v>
+        <v>18.5</v>
       </c>
       <c r="P26" t="n">
-        <v>24.3</v>
+        <v>24.2</v>
       </c>
       <c r="Q26" t="n">
-        <v>0.768</v>
+        <v>0.767</v>
       </c>
       <c r="R26" t="n">
         <v>13.1</v>
@@ -5077,7 +5144,7 @@
         <v>28.4</v>
       </c>
       <c r="T26" t="n">
-        <v>41.4</v>
+        <v>41.5</v>
       </c>
       <c r="U26" t="n">
         <v>20.3</v>
@@ -5092,28 +5159,28 @@
         <v>4.9</v>
       </c>
       <c r="Y26" t="n">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="Z26" t="n">
         <v>20.5</v>
       </c>
       <c r="AA26" t="n">
-        <v>21.2</v>
+        <v>21.1</v>
       </c>
       <c r="AB26" t="n">
-        <v>99.59999999999999</v>
+        <v>99.3</v>
       </c>
       <c r="AC26" t="n">
-        <v>4.9</v>
+        <v>4.6</v>
       </c>
       <c r="AD26" t="n">
-        <v>28</v>
+        <v>7</v>
       </c>
       <c r="AE26" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AF26" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AG26" t="n">
         <v>6</v>
@@ -5140,13 +5207,13 @@
         <v>7</v>
       </c>
       <c r="AO26" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="AP26" t="n">
         <v>17</v>
       </c>
       <c r="AQ26" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AR26" t="n">
         <v>1</v>
@@ -5164,7 +5231,7 @@
         <v>7</v>
       </c>
       <c r="AW26" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AX26" t="n">
         <v>13</v>
@@ -5173,7 +5240,7 @@
         <v>3</v>
       </c>
       <c r="AZ26" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="BA26" t="n">
         <v>12</v>
@@ -5194,7 +5261,7 @@
       </c>
       <c r="BF26" t="inlineStr">
         <is>
-          <t>4-9-2008-09</t>
+          <t>2009-04-09</t>
         </is>
       </c>
     </row>
@@ -5211,22 +5278,22 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="E27" t="n">
         <v>16</v>
       </c>
       <c r="F27" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="G27" t="n">
-        <v>0.205</v>
+        <v>0.208</v>
       </c>
       <c r="H27" t="n">
         <v>48.6</v>
       </c>
       <c r="I27" t="n">
-        <v>36.6</v>
+        <v>36.5</v>
       </c>
       <c r="J27" t="n">
         <v>81.40000000000001</v>
@@ -5235,22 +5302,22 @@
         <v>0.449</v>
       </c>
       <c r="L27" t="n">
-        <v>7.2</v>
+        <v>7.1</v>
       </c>
       <c r="M27" t="n">
         <v>19.4</v>
       </c>
       <c r="N27" t="n">
-        <v>0.368</v>
+        <v>0.367</v>
       </c>
       <c r="O27" t="n">
-        <v>20.8</v>
+        <v>20.9</v>
       </c>
       <c r="P27" t="n">
-        <v>26</v>
+        <v>26.1</v>
       </c>
       <c r="Q27" t="n">
-        <v>0.801</v>
+        <v>0.8</v>
       </c>
       <c r="R27" t="n">
         <v>10.1</v>
@@ -5277,25 +5344,25 @@
         <v>5.1</v>
       </c>
       <c r="Z27" t="n">
-        <v>23.4</v>
+        <v>23.6</v>
       </c>
       <c r="AA27" t="n">
-        <v>21.3</v>
+        <v>21.4</v>
       </c>
       <c r="AB27" t="n">
         <v>101.1</v>
       </c>
       <c r="AC27" t="n">
-        <v>-8.6</v>
+        <v>-8.5</v>
       </c>
       <c r="AD27" t="n">
-        <v>7</v>
+        <v>29</v>
       </c>
       <c r="AE27" t="n">
         <v>30</v>
       </c>
       <c r="AF27" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AG27" t="n">
         <v>30</v>
@@ -5334,7 +5401,7 @@
         <v>25</v>
       </c>
       <c r="AS27" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="AT27" t="n">
         <v>29</v>
@@ -5346,7 +5413,7 @@
         <v>26</v>
       </c>
       <c r="AW27" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="AX27" t="n">
         <v>25</v>
@@ -5361,7 +5428,7 @@
         <v>11</v>
       </c>
       <c r="BB27" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="BC27" t="n">
         <v>29</v>
@@ -5376,7 +5443,7 @@
       </c>
       <c r="BF27" t="inlineStr">
         <is>
-          <t>4-9-2008-09</t>
+          <t>2009-04-09</t>
         </is>
       </c>
     </row>
@@ -5474,28 +5541,28 @@
         <v>7</v>
       </c>
       <c r="AE28" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AF28" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AG28" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="AH28" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AI28" t="n">
         <v>11</v>
       </c>
       <c r="AJ28" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AK28" t="n">
         <v>7</v>
       </c>
       <c r="AL28" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AM28" t="n">
         <v>9</v>
@@ -5558,7 +5625,7 @@
       </c>
       <c r="BF28" t="inlineStr">
         <is>
-          <t>4-9-2008-09</t>
+          <t>2009-04-09</t>
         </is>
       </c>
     </row>
@@ -5686,7 +5753,7 @@
         <v>10</v>
       </c>
       <c r="AO29" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AP29" t="n">
         <v>26</v>
@@ -5740,7 +5807,7 @@
       </c>
       <c r="BF29" t="inlineStr">
         <is>
-          <t>4-9-2008-09</t>
+          <t>2009-04-09</t>
         </is>
       </c>
     </row>
@@ -5847,7 +5914,7 @@
         <v>10</v>
       </c>
       <c r="AH30" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AI30" t="n">
         <v>6</v>
@@ -5874,7 +5941,7 @@
         <v>3</v>
       </c>
       <c r="AQ30" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AR30" t="n">
         <v>11</v>
@@ -5922,7 +5989,7 @@
       </c>
       <c r="BF30" t="inlineStr">
         <is>
-          <t>4-9-2008-09</t>
+          <t>2009-04-09</t>
         </is>
       </c>
     </row>
@@ -6017,7 +6084,7 @@
         <v>-7.7</v>
       </c>
       <c r="AD31" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AE31" t="n">
         <v>28</v>
@@ -6056,7 +6123,7 @@
         <v>20</v>
       </c>
       <c r="AQ31" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AR31" t="n">
         <v>8</v>
@@ -6083,7 +6150,7 @@
         <v>23</v>
       </c>
       <c r="AZ31" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="BA31" t="n">
         <v>26</v>
@@ -6104,7 +6171,7 @@
       </c>
       <c r="BF31" t="inlineStr">
         <is>
-          <t>4-9-2008-09</t>
+          <t>2009-04-09</t>
         </is>
       </c>
     </row>
